--- a/salidas/empresas/CME.xlsx
+++ b/salidas/empresas/CME.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>41.40157699584961</v>
+        <v>41.40158462524414</v>
       </c>
       <c r="C3" t="n">
         <v>85.12000274658203</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>43.59690475463867</v>
+        <v>43.59689331054688</v>
       </c>
       <c r="C4" t="n">
         <v>89.5</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>44.61983108520508</v>
+        <v>44.61983871459961</v>
       </c>
       <c r="C5" t="n">
         <v>91.59999847412109</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.99288558959961</v>
+        <v>42.99287033081055</v>
       </c>
       <c r="C6" t="n">
         <v>88.26000213623047</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>47.91796493530273</v>
+        <v>47.91795349121094</v>
       </c>
       <c r="C7" t="n">
         <v>98.23000335693359</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>44.99596405029297</v>
+        <v>44.99596786499023</v>
       </c>
       <c r="C8" t="n">
         <v>92.23999786376953</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>42.92764282226562</v>
+        <v>42.92763519287109</v>
       </c>
       <c r="C9" t="n">
         <v>88</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>46.72566223144531</v>
+        <v>46.72565078735352</v>
       </c>
       <c r="C10" t="n">
         <v>95.65000152587891</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>48.94832611083984</v>
+        <v>48.94834899902344</v>
       </c>
       <c r="C11" t="n">
         <v>100.1999969482422</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>52.32881164550781</v>
+        <v>52.32881927490234</v>
       </c>
       <c r="C12" t="n">
         <v>107.120002746582</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>49.86124801635742</v>
+        <v>49.86121368408203</v>
       </c>
       <c r="C13" t="n">
         <v>101.9499969482422</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>55.09920120239258</v>
+        <v>55.09920883178711</v>
       </c>
       <c r="C14" t="n">
         <v>112.6600036621094</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>52.73697662353516</v>
+        <v>52.73698425292969</v>
       </c>
       <c r="C15" t="n">
         <v>107.8300018310547</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>52.16208648681641</v>
+        <v>52.16205978393555</v>
       </c>
       <c r="C16" t="n">
         <v>106.4919967651367</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>50.62302398681641</v>
+        <v>50.62305068969727</v>
       </c>
       <c r="C17" t="n">
         <v>103.3499984741211</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>52.01902770996094</v>
+        <v>52.01901245117188</v>
       </c>
       <c r="C18" t="n">
         <v>106.1999969482422</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>52.43180084228516</v>
+        <v>52.43181610107422</v>
       </c>
       <c r="C19" t="n">
         <v>106.8720016479492</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>54.21171188354492</v>
+        <v>54.21170043945312</v>
       </c>
       <c r="C20" t="n">
         <v>110.5</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>54.4373893737793</v>
+        <v>54.43739318847656</v>
       </c>
       <c r="C21" t="n">
         <v>110.9599990844727</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>57.71914672851562</v>
+        <v>57.71917343139648</v>
       </c>
       <c r="C22" t="n">
         <v>117.4700012207031</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>65.47268676757812</v>
+        <v>65.47271728515625</v>
       </c>
       <c r="C23" t="n">
         <v>133.25</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>64.720947265625</v>
+        <v>64.72095489501953</v>
       </c>
       <c r="C24" t="n">
         <v>131.7200012207031</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>67.49678802490234</v>
+        <v>67.49676513671875</v>
       </c>
       <c r="C25" t="n">
         <v>137.1999969482422</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>60.74713516235352</v>
+        <v>60.74710845947266</v>
       </c>
       <c r="C26" t="n">
         <v>123.4800033569336</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>50.50451278686523</v>
+        <v>50.50452423095703</v>
       </c>
       <c r="C27" t="n">
         <v>102.6600036621094</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>35.6143684387207</v>
+        <v>35.61436080932617</v>
       </c>
       <c r="C32" t="n">
         <v>72.0260009765625</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.34012985229492</v>
+        <v>37.34014129638672</v>
       </c>
       <c r="C34" t="n">
         <v>74.302001953125</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.35866165161133</v>
+        <v>28.35863494873047</v>
       </c>
       <c r="C35" t="n">
         <v>56.43000030517578</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>21.04131126403809</v>
+        <v>21.04132080078125</v>
       </c>
       <c r="C37" t="n">
         <v>41.62200164794922</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.58346748352051</v>
+        <v>17.58346366882324</v>
       </c>
       <c r="C38" t="n">
         <v>34.78200149536133</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>18.44186019897461</v>
+        <v>18.44185829162598</v>
       </c>
       <c r="C39" t="n">
         <v>36.47999954223633</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>25.06971549987793</v>
+        <v>25.0697135925293</v>
       </c>
       <c r="C40" t="n">
         <v>49.27799987792969</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>22.52193832397461</v>
+        <v>22.52193450927734</v>
       </c>
       <c r="C41" t="n">
         <v>44.27000045776367</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>32.72624969482422</v>
+        <v>32.72625732421875</v>
       </c>
       <c r="C42" t="n">
         <v>64.3280029296875</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>31.76493072509766</v>
+        <v>31.76492500305176</v>
       </c>
       <c r="C43" t="n">
         <v>62.2239990234375</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.46816444396973</v>
+        <v>28.4681568145752</v>
       </c>
       <c r="C44" t="n">
         <v>55.76599884033203</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>29.71479988098145</v>
+        <v>29.71479415893555</v>
       </c>
       <c r="C45" t="n">
         <v>58.20800018310547</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>31.60013580322266</v>
+        <v>31.60013198852539</v>
       </c>
       <c r="C46" t="n">
         <v>61.63800048828125</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>31.02797698974609</v>
+        <v>31.02798271179199</v>
       </c>
       <c r="C47" t="n">
         <v>60.52199935913086</v>
@@ -1368,7 +1380,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1393,7 +1405,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>29.51382446289062</v>
+        <v>29.5138111114502</v>
       </c>
       <c r="C50" t="n">
         <v>57.36399841308594</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>31.0439510345459</v>
+        <v>31.0439453125</v>
       </c>
       <c r="C51" t="n">
         <v>60.3380012512207</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.64883804321289</v>
+        <v>32.64884185791016</v>
       </c>
       <c r="C52" t="n">
         <v>63.22200012207031</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>34.00803756713867</v>
+        <v>34.00804138183594</v>
       </c>
       <c r="C53" t="n">
         <v>65.85399627685547</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.70459365844727</v>
+        <v>32.70462417602539</v>
       </c>
       <c r="C54" t="n">
         <v>63.33000183105469</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>29.19142150878906</v>
+        <v>29.19142913818359</v>
       </c>
       <c r="C55" t="n">
         <v>56.31000137329102</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>28.90631103515625</v>
+        <v>28.90630340576172</v>
       </c>
       <c r="C56" t="n">
         <v>55.7599983215332</v>
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.72951126098633</v>
+        <v>25.72951889038086</v>
       </c>
       <c r="C57" t="n">
         <v>49.63199996948242</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.12446022033691</v>
+        <v>27.12444877624512</v>
       </c>
       <c r="C58" t="n">
         <v>52.09000015258789</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.16548538208008</v>
+        <v>30.16548347473145</v>
       </c>
       <c r="C59" t="n">
         <v>57.93000030517578</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>29.9998836517334</v>
+        <v>29.99989891052246</v>
       </c>
       <c r="C60" t="n">
         <v>57.61199951171875</v>
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1718,7 +1730,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>32.53730392456055</v>
+        <v>32.53730010986328</v>
       </c>
       <c r="C63" t="n">
         <v>62.25600051879883</v>
@@ -1772,11 +1784,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>31.66613960266113</v>
+        <v>31.66614532470703</v>
       </c>
       <c r="C64" t="n">
         <v>60.31000137329102</v>
@@ -1801,11 +1813,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>31.05918121337891</v>
+        <v>31.05917739868164</v>
       </c>
       <c r="C65" t="n">
         <v>59.15399932861328</v>
@@ -1830,11 +1842,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>30.00802040100098</v>
+        <v>30.00801467895508</v>
       </c>
       <c r="C66" t="n">
         <v>57.15200042724609</v>
@@ -1859,11 +1871,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.77914619445801</v>
+        <v>30.77914237976074</v>
       </c>
       <c r="C67" t="n">
         <v>58.31800079345703</v>
@@ -1888,11 +1900,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>30.52581214904785</v>
+        <v>30.52579689025879</v>
       </c>
       <c r="C68" t="n">
         <v>57.8380012512207</v>
@@ -1917,11 +1929,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>28.19617462158203</v>
+        <v>28.19618034362793</v>
       </c>
       <c r="C69" t="n">
         <v>53.42399978637695</v>
@@ -1946,11 +1958,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>26.15276718139648</v>
+        <v>26.15276145935059</v>
       </c>
       <c r="C70" t="n">
         <v>49.27999877929688</v>
@@ -1975,11 +1987,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>29.24778366088867</v>
+        <v>29.24777793884277</v>
       </c>
       <c r="C71" t="n">
         <v>55.11199951171875</v>
@@ -2004,7 +2016,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2033,11 +2045,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>26.01546859741211</v>
+        <v>26.01545524597168</v>
       </c>
       <c r="C73" t="n">
         <v>48.73400115966797</v>
@@ -2062,11 +2074,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>25.57132911682129</v>
+        <v>25.57131195068359</v>
       </c>
       <c r="C74" t="n">
         <v>47.90200042724609</v>
@@ -2091,11 +2103,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>30.90742874145508</v>
+        <v>30.90746116638184</v>
       </c>
       <c r="C75" t="n">
         <v>57.89799880981445</v>
@@ -2120,7 +2132,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2149,11 +2161,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>28.93065643310547</v>
+        <v>28.93065071105957</v>
       </c>
       <c r="C77" t="n">
         <v>53.16400146484375</v>
@@ -2178,11 +2190,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>28.03277206420898</v>
+        <v>28.03276634216309</v>
       </c>
       <c r="C78" t="n">
         <v>51.51399993896484</v>
@@ -2207,11 +2219,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>29.42455863952637</v>
+        <v>29.4245662689209</v>
       </c>
       <c r="C79" t="n">
         <v>53.62200164794922</v>
@@ -2236,11 +2248,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>28.59485626220703</v>
+        <v>28.59485816955566</v>
       </c>
       <c r="C80" t="n">
         <v>52.11000061035156</v>
@@ -2265,11 +2277,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>30.1258373260498</v>
+        <v>30.12584686279297</v>
       </c>
       <c r="C81" t="n">
         <v>54.90000152587891</v>
@@ -2294,11 +2306,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>31.69519805908203</v>
+        <v>31.69520378112793</v>
       </c>
       <c r="C82" t="n">
         <v>57.29000091552734</v>
@@ -2323,11 +2335,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>30.94279861450195</v>
+        <v>30.94280242919922</v>
       </c>
       <c r="C83" t="n">
         <v>55.93000030517578</v>
@@ -2352,11 +2364,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>30.57766151428223</v>
+        <v>30.57765007019043</v>
       </c>
       <c r="C84" t="n">
         <v>55.27000045776367</v>
@@ -2381,11 +2393,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>28.97868156433105</v>
+        <v>28.97868347167969</v>
       </c>
       <c r="C85" t="n">
         <v>50.66999816894531</v>
@@ -2410,11 +2422,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>33.07928085327148</v>
+        <v>33.07928848266602</v>
       </c>
       <c r="C86" t="n">
         <v>57.84000015258789</v>
@@ -2439,11 +2451,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>34.12586212158203</v>
+        <v>34.12587738037109</v>
       </c>
       <c r="C87" t="n">
         <v>59.66999816894531</v>
@@ -2468,11 +2480,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>35.37932586669922</v>
+        <v>35.37931442260742</v>
       </c>
       <c r="C88" t="n">
         <v>61.40999984741211</v>
@@ -2497,7 +2509,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>39.13561630249023</v>
+        <v>39.13561248779297</v>
       </c>
       <c r="C90" t="n">
         <v>67.93000030517578</v>
@@ -2555,11 +2567,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>44.04217529296875</v>
+        <v>44.04216003417969</v>
       </c>
       <c r="C91" t="n">
         <v>75.94999694824219</v>
@@ -2584,11 +2596,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>42.94618988037109</v>
+        <v>42.94620513916016</v>
       </c>
       <c r="C92" t="n">
         <v>74.05999755859375</v>
@@ -2613,11 +2625,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>41.23553085327148</v>
+        <v>41.23552703857422</v>
       </c>
       <c r="C93" t="n">
         <v>71.11000061035156</v>
@@ -2642,11 +2654,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>43.10619354248047</v>
+        <v>43.1061897277832</v>
       </c>
       <c r="C94" t="n">
         <v>73.87999725341797</v>
@@ -2671,7 +2683,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2700,11 +2712,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>47.81471633911133</v>
+        <v>47.81473159790039</v>
       </c>
       <c r="C96" t="n">
         <v>81.94999694824219</v>
@@ -2729,11 +2741,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>47.52699661254883</v>
+        <v>47.52700424194336</v>
       </c>
       <c r="C97" t="n">
         <v>78.45999908447266</v>
@@ -2758,11 +2770,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>45.28572845458984</v>
+        <v>45.28575134277344</v>
       </c>
       <c r="C98" t="n">
         <v>74.76000213623047</v>
@@ -2787,7 +2799,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2816,11 +2828,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>45.11493301391602</v>
+        <v>45.11493682861328</v>
       </c>
       <c r="C100" t="n">
         <v>74.01999664306641</v>
@@ -2845,11 +2857,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>42.90248107910156</v>
+        <v>42.90246200561523</v>
       </c>
       <c r="C101" t="n">
         <v>70.38999938964844</v>
@@ -2874,7 +2886,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2903,11 +2915,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>43.53818130493164</v>
+        <v>43.53817749023438</v>
       </c>
       <c r="C103" t="n">
         <v>70.94999694824219</v>
@@ -2932,7 +2944,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2961,11 +2973,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>46.97459030151367</v>
+        <v>46.97460174560547</v>
       </c>
       <c r="C105" t="n">
         <v>76.55000305175781</v>
@@ -2990,11 +3002,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>49.37063980102539</v>
+        <v>49.37063598632812</v>
       </c>
       <c r="C106" t="n">
         <v>79.95999908447266</v>
@@ -3019,11 +3031,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>51.74778366088867</v>
+        <v>51.74779510498047</v>
       </c>
       <c r="C107" t="n">
         <v>83.80999755859375</v>
@@ -3048,11 +3060,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.26026916503906</v>
+        <v>52.26028060913086</v>
       </c>
       <c r="C108" t="n">
         <v>84.63999938964844</v>
@@ -3077,7 +3089,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3106,11 +3118,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>54.11550140380859</v>
+        <v>54.11551284790039</v>
       </c>
       <c r="C110" t="n">
         <v>85.30000305175781</v>
@@ -3135,11 +3147,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>60.85931396484375</v>
+        <v>60.85933685302734</v>
       </c>
       <c r="C111" t="n">
         <v>95.93000030517578</v>
@@ -3164,7 +3176,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3193,11 +3205,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>57.97396087646484</v>
+        <v>57.97393035888672</v>
       </c>
       <c r="C113" t="n">
         <v>90.91000366210938</v>
@@ -3222,11 +3234,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>60.07202529907227</v>
+        <v>60.07201766967773</v>
       </c>
       <c r="C114" t="n">
         <v>94.19999694824219</v>
@@ -3251,11 +3263,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>59.65589904785156</v>
+        <v>59.65588760375977</v>
       </c>
       <c r="C115" t="n">
         <v>93.05999755859375</v>
@@ -3280,7 +3292,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3309,11 +3321,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>60.54055786132812</v>
+        <v>60.54053497314453</v>
       </c>
       <c r="C117" t="n">
         <v>94.44000244140625</v>
@@ -3338,11 +3350,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>59.77413177490234</v>
+        <v>59.77410507202148</v>
       </c>
       <c r="C118" t="n">
         <v>92.73999786376953</v>
@@ -3367,11 +3379,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>60.88915634155273</v>
+        <v>60.88915252685547</v>
       </c>
       <c r="C119" t="n">
         <v>94.47000122070312</v>
@@ -3396,11 +3408,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>62.93877029418945</v>
+        <v>62.93876647949219</v>
       </c>
       <c r="C120" t="n">
         <v>97.65000152587891</v>
@@ -3425,7 +3437,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3454,11 +3466,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>60.04267120361328</v>
+        <v>60.04262924194336</v>
       </c>
       <c r="C122" t="n">
         <v>89.84999847412109</v>
@@ -3483,11 +3495,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>61.10518264770508</v>
+        <v>61.10517883300781</v>
       </c>
       <c r="C123" t="n">
         <v>91.44000244140625</v>
@@ -3512,11 +3524,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>64.60001373291016</v>
+        <v>64.60003662109375</v>
       </c>
       <c r="C124" t="n">
         <v>96.05000305175781</v>
@@ -3541,11 +3553,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>61.81558609008789</v>
+        <v>61.81561660766602</v>
       </c>
       <c r="C125" t="n">
         <v>91.91000366210938</v>
@@ -3570,11 +3582,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>65.83754730224609</v>
+        <v>65.83753967285156</v>
       </c>
       <c r="C126" t="n">
         <v>97.88999938964844</v>
@@ -3599,11 +3611,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>65.91981506347656</v>
+        <v>65.91982269287109</v>
       </c>
       <c r="C127" t="n">
         <v>97.40000152587891</v>
@@ -3628,11 +3640,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>69.19551086425781</v>
+        <v>69.19550323486328</v>
       </c>
       <c r="C128" t="n">
         <v>102.2399978637695</v>
@@ -3657,11 +3669,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>73.33070373535156</v>
+        <v>73.33072662353516</v>
       </c>
       <c r="C129" t="n">
         <v>108.3499984741211</v>
@@ -3686,11 +3698,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>71.13488006591797</v>
+        <v>71.13487243652344</v>
       </c>
       <c r="C130" t="n">
         <v>104.5199966430664</v>
@@ -3715,11 +3727,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>68.12671661376953</v>
+        <v>68.12667846679688</v>
       </c>
       <c r="C131" t="n">
         <v>100.0999984741211</v>
@@ -3744,11 +3756,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>76.84500885009766</v>
+        <v>76.84503936767578</v>
       </c>
       <c r="C132" t="n">
         <v>112.9100036621094</v>
@@ -3773,11 +3785,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>81.086669921875</v>
+        <v>81.08665466308594</v>
       </c>
       <c r="C133" t="n">
         <v>115.3499984741211</v>
@@ -3802,11 +3814,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>85.11465454101562</v>
+        <v>85.11463165283203</v>
       </c>
       <c r="C134" t="n">
         <v>121.0800018310547</v>
@@ -3831,11 +3843,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>85.38179016113281</v>
+        <v>85.38176727294922</v>
       </c>
       <c r="C135" t="n">
         <v>121.4599990844727</v>
@@ -3860,11 +3872,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>83.96034240722656</v>
+        <v>83.96038818359375</v>
       </c>
       <c r="C136" t="n">
         <v>118.8000030517578</v>
@@ -3889,11 +3901,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>82.11576843261719</v>
+        <v>82.11579132080078</v>
       </c>
       <c r="C137" t="n">
         <v>116.1900024414062</v>
@@ -3918,7 +3930,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3947,7 +3959,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3976,11 +3988,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>87.15080261230469</v>
+        <v>87.15079498291016</v>
       </c>
       <c r="C140" t="n">
         <v>122.620002746582</v>
@@ -4005,11 +4017,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>89.41095733642578</v>
+        <v>89.41094207763672</v>
       </c>
       <c r="C141" t="n">
         <v>125.8000030517578</v>
@@ -4034,11 +4046,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>96.93120574951172</v>
+        <v>96.93119812011719</v>
       </c>
       <c r="C142" t="n">
         <v>135.6799926757812</v>
@@ -4063,11 +4075,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>97.99569702148438</v>
+        <v>97.99568939208984</v>
       </c>
       <c r="C143" t="n">
         <v>137.1699981689453</v>
@@ -4092,11 +4104,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>106.8329544067383</v>
+        <v>106.8329162597656</v>
       </c>
       <c r="C144" t="n">
         <v>149.5399932861328</v>
@@ -4121,11 +4133,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>107.3142471313477</v>
+        <v>107.3142700195312</v>
       </c>
       <c r="C145" t="n">
         <v>146.0500030517578</v>
@@ -4150,11 +4162,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>112.7736434936523</v>
+        <v>112.7736511230469</v>
       </c>
       <c r="C146" t="n">
         <v>153.4799957275391</v>
@@ -4179,11 +4191,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>122.0906295776367</v>
+        <v>122.0906753540039</v>
       </c>
       <c r="C147" t="n">
         <v>166.1600036621094</v>
@@ -4208,11 +4220,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>119.3384170532227</v>
+        <v>119.3384552001953</v>
       </c>
       <c r="C148" t="n">
         <v>161.7400054931641</v>
@@ -4237,11 +4249,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>116.3428115844727</v>
+        <v>116.3428039550781</v>
       </c>
       <c r="C149" t="n">
         <v>157.6799926757812</v>
@@ -4266,11 +4278,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>120.1943511962891</v>
+        <v>120.1943588256836</v>
       </c>
       <c r="C150" t="n">
         <v>162.8999938964844</v>
@@ -4295,11 +4307,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>121.4367599487305</v>
+        <v>121.4367141723633</v>
       </c>
       <c r="C151" t="n">
         <v>163.9199981689453</v>
@@ -4324,11 +4336,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>117.8807678222656</v>
+        <v>117.8807754516602</v>
       </c>
       <c r="C152" t="n">
         <v>159.1199951171875</v>
@@ -4353,11 +4365,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>129.4451599121094</v>
+        <v>129.4451904296875</v>
       </c>
       <c r="C153" t="n">
         <v>174.7299957275391</v>
@@ -4382,11 +4394,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>126.6073989868164</v>
+        <v>126.607421875</v>
       </c>
       <c r="C154" t="n">
         <v>170.2100067138672</v>
@@ -4411,11 +4423,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>136.2995300292969</v>
+        <v>136.2995147705078</v>
       </c>
       <c r="C155" t="n">
         <v>183.2400054931641</v>
@@ -4440,11 +4452,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>141.3873596191406</v>
+        <v>141.3872985839844</v>
       </c>
       <c r="C156" t="n">
         <v>190.0800018310547</v>
@@ -4469,11 +4481,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>141.8107147216797</v>
+        <v>141.8106994628906</v>
       </c>
       <c r="C157" t="n">
         <v>188.1199951171875</v>
@@ -4498,11 +4510,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>137.4082946777344</v>
+        <v>137.4083099365234</v>
       </c>
       <c r="C158" t="n">
         <v>182.2799987792969</v>
@@ -4527,11 +4539,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>137.1294097900391</v>
+        <v>137.12939453125</v>
       </c>
       <c r="C159" t="n">
         <v>181.9100036621094</v>
@@ -4556,11 +4568,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>124.6018447875977</v>
+        <v>124.6018142700195</v>
       </c>
       <c r="C160" t="n">
         <v>164.5800018310547</v>
@@ -4585,11 +4597,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>135.443359375</v>
+        <v>135.4433441162109</v>
       </c>
       <c r="C161" t="n">
         <v>178.8999938964844</v>
@@ -4614,7 +4626,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4643,11 +4655,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>147.5093841552734</v>
+        <v>147.5093536376953</v>
       </c>
       <c r="C163" t="n">
         <v>194.1100006103516</v>
@@ -4672,11 +4684,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>147.7450103759766</v>
+        <v>147.7449340820312</v>
       </c>
       <c r="C164" t="n">
         <v>194.4199981689453</v>
@@ -4701,11 +4713,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>165.1244659423828</v>
+        <v>165.1244506835938</v>
       </c>
       <c r="C165" t="n">
         <v>217.2899932861328</v>
@@ -4730,7 +4742,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4759,11 +4771,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>156.8824615478516</v>
+        <v>156.8823547363281</v>
       </c>
       <c r="C167" t="n">
         <v>205.75</v>
@@ -4788,11 +4800,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>154.5796661376953</v>
+        <v>154.5796508789062</v>
       </c>
       <c r="C168" t="n">
         <v>202.7299957275391</v>
@@ -4817,11 +4829,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>155.5182800292969</v>
+        <v>155.5182952880859</v>
       </c>
       <c r="C169" t="n">
         <v>200.7200012207031</v>
@@ -4846,11 +4858,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>168.2173309326172</v>
+        <v>168.2173004150391</v>
       </c>
       <c r="C170" t="n">
         <v>217.1100006103516</v>
@@ -4875,11 +4887,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>154.0462036132812</v>
+        <v>154.0461730957031</v>
       </c>
       <c r="C171" t="n">
         <v>198.8200073242188</v>
@@ -4904,11 +4916,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>134.4996948242188</v>
+        <v>134.4997100830078</v>
       </c>
       <c r="C172" t="n">
         <v>172.9100036621094</v>
@@ -4933,7 +4945,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4962,11 +4974,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>142.0371551513672</v>
+        <v>142.0371856689453</v>
       </c>
       <c r="C174" t="n">
         <v>182.6000061035156</v>
@@ -4991,11 +5003,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>126.9962387084961</v>
+        <v>126.9962005615234</v>
       </c>
       <c r="C175" t="n">
         <v>162.5399932861328</v>
@@ -5020,11 +5032,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>129.8402709960938</v>
+        <v>129.8403015136719</v>
       </c>
       <c r="C176" t="n">
         <v>166.1799926757812</v>
@@ -5049,11 +5061,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>137.4113006591797</v>
+        <v>137.4112854003906</v>
       </c>
       <c r="C177" t="n">
         <v>175.8699951171875</v>
@@ -5078,11 +5090,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>131.3919067382812</v>
+        <v>131.3919677734375</v>
       </c>
       <c r="C178" t="n">
         <v>167.3099975585938</v>
@@ -5107,11 +5119,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>118.3635177612305</v>
+        <v>118.3634490966797</v>
       </c>
       <c r="C179" t="n">
         <v>150.7200012207031</v>
@@ -5136,7 +5148,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5165,11 +5177,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>145.6524353027344</v>
+        <v>145.6524505615234</v>
       </c>
       <c r="C181" t="n">
         <v>182.0500030517578</v>
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>145.4044189453125</v>
+        <v>145.4044036865234</v>
       </c>
       <c r="C182" t="n">
         <v>181.7400054931641</v>
@@ -5223,11 +5235,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>159.7736663818359</v>
+        <v>159.7736206054688</v>
       </c>
       <c r="C183" t="n">
         <v>199.6999969482422</v>
@@ -5252,11 +5264,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>164.0879211425781</v>
+        <v>164.0878448486328</v>
       </c>
       <c r="C184" t="n">
         <v>204.2299957275391</v>
@@ -5281,11 +5293,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>162.2881622314453</v>
+        <v>162.2881927490234</v>
       </c>
       <c r="C185" t="n">
         <v>201.9900054931641</v>
@@ -5310,11 +5322,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>175.761962890625</v>
+        <v>175.7619781494141</v>
       </c>
       <c r="C186" t="n">
         <v>218.7599945068359</v>
@@ -5339,11 +5351,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>171.5865936279297</v>
+        <v>171.5865631103516</v>
       </c>
       <c r="C187" t="n">
         <v>212.6799926757812</v>
@@ -5368,7 +5380,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5397,11 +5409,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>162.7442932128906</v>
+        <v>162.7442169189453</v>
       </c>
       <c r="C189" t="n">
         <v>201.7200012207031</v>
@@ -5426,11 +5438,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>156.7437896728516</v>
+        <v>156.7438049316406</v>
       </c>
       <c r="C190" t="n">
         <v>193.3800048828125</v>
@@ -5455,11 +5467,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>178.766357421875</v>
+        <v>178.7664031982422</v>
       </c>
       <c r="C191" t="n">
         <v>220.5500030517578</v>
@@ -5484,11 +5496,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>178.7420654296875</v>
+        <v>178.7420806884766</v>
       </c>
       <c r="C192" t="n">
         <v>220.5200042724609</v>
@@ -5513,7 +5525,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5542,11 +5554,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>189.4342956542969</v>
+        <v>189.4342651367188</v>
       </c>
       <c r="C194" t="n">
         <v>229.5</v>
@@ -5571,11 +5583,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>195.2369689941406</v>
+        <v>195.2369842529297</v>
       </c>
       <c r="C195" t="n">
         <v>236.5299987792969</v>
@@ -5600,11 +5612,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>197.2202453613281</v>
+        <v>197.2202606201172</v>
       </c>
       <c r="C196" t="n">
         <v>237.8600006103516</v>
@@ -5629,11 +5641,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>181.8644866943359</v>
+        <v>181.864501953125</v>
       </c>
       <c r="C197" t="n">
         <v>219.3399963378906</v>
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>164.8587341308594</v>
+        <v>164.8587493896484</v>
       </c>
       <c r="C198" t="n">
         <v>198.8300018310547</v>
@@ -5687,11 +5699,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>170.5805816650391</v>
+        <v>170.5805969238281</v>
       </c>
       <c r="C199" t="n">
         <v>204.6999969482422</v>
@@ -5716,11 +5728,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>166.2306060791016</v>
+        <v>166.2306365966797</v>
       </c>
       <c r="C200" t="n">
         <v>199.4799957275391</v>
@@ -5745,11 +5757,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>163.0056610107422</v>
+        <v>163.0056762695312</v>
       </c>
       <c r="C201" t="n">
         <v>195.6100006103516</v>
@@ -5774,7 +5786,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5803,11 +5815,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>145.1388092041016</v>
+        <v>145.1387939453125</v>
       </c>
       <c r="C203" t="n">
         <v>173.3000030517578</v>
@@ -5832,11 +5844,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>147.8187713623047</v>
+        <v>147.8187866210938</v>
       </c>
       <c r="C204" t="n">
         <v>176.5</v>
@@ -5861,11 +5873,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>145.4140472412109</v>
+        <v>145.4140930175781</v>
       </c>
       <c r="C205" t="n">
         <v>168.1600036621094</v>
@@ -5890,11 +5902,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>152.7642974853516</v>
+        <v>152.7643127441406</v>
       </c>
       <c r="C206" t="n">
         <v>176.6600036621094</v>
@@ -5919,11 +5931,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>160.2875061035156</v>
+        <v>160.2875213623047</v>
       </c>
       <c r="C207" t="n">
         <v>185.3600006103516</v>
@@ -5948,11 +5960,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>166.6217803955078</v>
+        <v>166.6217956542969</v>
       </c>
       <c r="C208" t="n">
         <v>191.5200042724609</v>
@@ -5977,11 +5989,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>161.6192932128906</v>
+        <v>161.6193084716797</v>
       </c>
       <c r="C209" t="n">
         <v>185.7700042724609</v>
@@ -6006,11 +6018,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>155.5119323730469</v>
+        <v>155.5119018554688</v>
       </c>
       <c r="C210" t="n">
         <v>178.75</v>
@@ -6035,7 +6047,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6064,11 +6076,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>174.1439056396484</v>
+        <v>174.1438598632812</v>
       </c>
       <c r="C212" t="n">
         <v>198.9600067138672</v>
@@ -6093,7 +6105,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6122,7 +6134,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6151,11 +6163,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>187.8499145507812</v>
+        <v>187.8499450683594</v>
       </c>
       <c r="C215" t="n">
         <v>213.4600067138672</v>
@@ -6180,7 +6192,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6209,11 +6221,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>190.9567718505859</v>
+        <v>190.9567565917969</v>
       </c>
       <c r="C217" t="n">
         <v>210.6000061035156</v>
@@ -6238,7 +6250,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6267,11 +6279,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>199.7973327636719</v>
+        <v>199.7973480224609</v>
       </c>
       <c r="C219" t="n">
         <v>220.3500061035156</v>
@@ -6296,11 +6308,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>196.2365417480469</v>
+        <v>196.2365112304688</v>
       </c>
       <c r="C220" t="n">
         <v>215.2899932861328</v>
@@ -6325,11 +6337,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>191.0865478515625</v>
+        <v>191.0865936279297</v>
       </c>
       <c r="C221" t="n">
         <v>209.6399993896484</v>
@@ -6354,11 +6366,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>185.0159606933594</v>
+        <v>185.0159912109375</v>
       </c>
       <c r="C222" t="n">
         <v>202.9799957275391</v>
@@ -6383,7 +6395,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6412,11 +6424,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>177.5799407958984</v>
+        <v>177.5799560546875</v>
       </c>
       <c r="C224" t="n">
         <v>193.7100067138672</v>
@@ -6441,11 +6453,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>197.7755126953125</v>
+        <v>197.7755279541016</v>
       </c>
       <c r="C225" t="n">
         <v>215.7400054931641</v>
@@ -6470,11 +6482,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>203.3371276855469</v>
+        <v>203.3371429443359</v>
       </c>
       <c r="C226" t="n">
         <v>220.6499938964844</v>
@@ -6499,11 +6511,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>207.6775665283203</v>
+        <v>207.6775817871094</v>
       </c>
       <c r="C227" t="n">
         <v>225.3600006103516</v>
@@ -6528,11 +6540,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>219.3258209228516</v>
+        <v>219.3258361816406</v>
       </c>
       <c r="C228" t="n">
         <v>238</v>
@@ -6557,11 +6569,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>220.3851928710938</v>
+        <v>220.3851776123047</v>
       </c>
       <c r="C229" t="n">
         <v>232.2299957275391</v>
@@ -6586,11 +6598,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>224.4563751220703</v>
+        <v>224.4563903808594</v>
       </c>
       <c r="C230" t="n">
         <v>236.5200042724609</v>
@@ -6615,11 +6627,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>240.8265228271484</v>
+        <v>240.8265533447266</v>
       </c>
       <c r="C231" t="n">
         <v>253.7700042724609</v>
@@ -6644,11 +6656,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>253.0038604736328</v>
+        <v>253.0038757324219</v>
       </c>
       <c r="C232" t="n">
         <v>265.2900085449219</v>
@@ -6673,11 +6685,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>264.2478637695312</v>
+        <v>264.2478332519531</v>
       </c>
       <c r="C233" t="n">
         <v>277.0799865722656</v>
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6731,7 +6743,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6760,7 +6772,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6789,11 +6801,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>255.3311767578125</v>
+        <v>255.3312072753906</v>
       </c>
       <c r="C237" t="n">
         <v>266.510009765625</v>
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6847,7 +6859,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6876,7 +6888,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6905,7 +6917,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6934,7 +6946,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6963,7 +6975,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6992,7 +7004,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7050,7 +7062,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7079,7 +7091,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7108,7 +7120,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7137,7 +7149,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7166,32 +7178,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>270.7999877929688</v>
+        <v>268.9100036621094</v>
       </c>
       <c r="C250" t="n">
-        <v>270.7999877929688</v>
+        <v>268.9100036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>28893200</v>
+        <v>30148200</v>
       </c>
       <c r="E250" t="n">
         <v>11.79</v>
       </c>
       <c r="F250" t="n">
-        <v>22.96861643706266</v>
+        <v>22.8083124395343</v>
       </c>
       <c r="G250" t="n">
         <v>360684000</v>
       </c>
       <c r="H250" t="n">
-        <v>97673222797.11914</v>
+        <v>96991535760.86426</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08010668618513712</v>
+        <v>0.08358618624613234</v>
       </c>
     </row>
   </sheetData>
@@ -7223,75 +7235,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40060</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40060</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7495,13 +7507,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7528,7 +7540,7 @@
       <c r="I7" t="n">
         <v>2.482</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K7" t="n">
@@ -7541,13 +7553,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7574,7 +7586,7 @@
       <c r="I8" t="n">
         <v>2.606</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K8" t="n">
@@ -7587,13 +7599,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7620,7 +7632,7 @@
       <c r="I9" t="n">
         <v>2.762</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K9" t="n">
@@ -7633,13 +7645,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7666,7 +7678,7 @@
       <c r="I10" t="n">
         <v>2.886</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7679,13 +7691,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7712,7 +7724,7 @@
       <c r="I11" t="n">
         <v>2.864</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7725,13 +7737,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7758,7 +7770,7 @@
       <c r="I12" t="n">
         <v>3.502</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K12" t="n">
@@ -7771,13 +7783,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7804,7 +7816,7 @@
       <c r="I13" t="n">
         <v>3.556</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7817,13 +7829,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7850,7 +7862,7 @@
       <c r="I14" t="n">
         <v>3.772</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="K14" t="n">
@@ -7863,13 +7875,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7896,7 +7908,7 @@
       <c r="I15" t="n">
         <v>5.436</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K15" t="n">
@@ -7909,13 +7921,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7942,7 +7954,7 @@
       <c r="I16" t="n">
         <v>4.878</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K16" t="n">
@@ -7955,13 +7967,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7988,7 +8000,7 @@
       <c r="I17" t="n">
         <v>4.742</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K17" t="n">
@@ -8001,13 +8013,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8034,7 +8046,7 @@
       <c r="I18" t="n">
         <v>4.454</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="K18" t="n">
@@ -8047,13 +8059,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8080,7 +8092,7 @@
       <c r="I19" t="n">
         <v>2.704</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K19" t="n">
@@ -8093,13 +8105,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8126,7 +8138,7 @@
       <c r="I20" t="n">
         <v>2.61</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K20" t="n">
@@ -8139,13 +8151,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8172,7 +8184,7 @@
       <c r="I21" t="n">
         <v>2.8</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K21" t="n">
@@ -8185,13 +8197,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8218,7 +8230,7 @@
       <c r="I22" t="n">
         <v>2.85</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="K22" t="n">
@@ -8231,13 +8243,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8264,7 +8276,7 @@
       <c r="I23" t="n">
         <v>2.93</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="K23" t="n">
@@ -8277,13 +8289,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8310,7 +8322,7 @@
       <c r="I24" t="n">
         <v>3.01</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K24" t="n">
@@ -8323,13 +8335,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8356,7 +8368,7 @@
       <c r="I25" t="n">
         <v>2.87</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="K25" t="n">
@@ -8369,13 +8381,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8402,7 +8414,7 @@
       <c r="I26" t="n">
         <v>3.02</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K26" t="n">
@@ -8415,13 +8427,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8448,7 +8460,7 @@
       <c r="I27" t="n">
         <v>3.35</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K27" t="n">
@@ -8461,13 +8473,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8494,7 +8506,7 @@
       <c r="I28" t="n">
         <v>3.54</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K28" t="n">
@@ -8507,13 +8519,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8540,7 +8552,7 @@
       <c r="I29" t="n">
         <v>3.53</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K29" t="n">
@@ -8553,13 +8565,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8586,7 +8598,7 @@
       <c r="I30" t="n">
         <v>3.73</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="K30" t="n">
@@ -8599,13 +8611,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8632,7 +8644,7 @@
       <c r="I31" t="n">
         <v>3.68</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K31" t="n">
@@ -8645,13 +8657,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8678,7 +8690,7 @@
       <c r="I32" t="n">
         <v>3.79</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K32" t="n">
@@ -8691,13 +8703,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8724,7 +8736,7 @@
       <c r="I33" t="n">
         <v>3.96</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K33" t="n">
@@ -8737,13 +8749,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8770,7 +8782,7 @@
       <c r="I34" t="n">
         <v>4.29</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K34" t="n">
@@ -8783,13 +8795,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8816,7 +8828,7 @@
       <c r="I35" t="n">
         <v>4.529999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="K35" t="n">
@@ -8829,13 +8841,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8862,7 +8874,7 @@
       <c r="I36" t="n">
         <v>4.62</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K36" t="n">
@@ -8875,13 +8887,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8908,7 +8920,7 @@
       <c r="I37" t="n">
         <v>4.89</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K37" t="n">
@@ -8921,13 +8933,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8954,7 +8966,7 @@
       <c r="I38" t="n">
         <v>4.41</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K38" t="n">
@@ -8967,13 +8979,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9000,7 +9012,7 @@
       <c r="I39" t="n">
         <v>11.94</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="K39" t="n">
@@ -9013,13 +9025,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9046,7 +9058,7 @@
       <c r="I40" t="n">
         <v>12.52</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K40" t="n">
@@ -9059,13 +9071,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9092,7 +9104,7 @@
       <c r="I41" t="n">
         <v>12.96</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K41" t="n">
@@ -9105,13 +9117,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9138,7 +9150,7 @@
       <c r="I42" t="n">
         <v>13.26</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K42" t="n">
@@ -9151,13 +9163,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9184,7 +9196,7 @@
       <c r="I43" t="n">
         <v>5.72</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K43" t="n">
@@ -9197,13 +9209,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9230,7 +9242,7 @@
       <c r="I44" t="n">
         <v>5.35</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K44" t="n">
@@ -9243,13 +9255,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9276,7 +9288,7 @@
       <c r="I45" t="n">
         <v>5.12</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K45" t="n">
@@ -9289,13 +9301,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9322,7 +9334,7 @@
       <c r="I46" t="n">
         <v>5.69</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K46" t="n">
@@ -9335,13 +9347,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9368,7 +9380,7 @@
       <c r="I47" t="n">
         <v>5.91</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="K47" t="n">
@@ -9381,13 +9393,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9414,7 +9426,7 @@
       <c r="I48" t="n">
         <v>6.66</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9427,13 +9439,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9460,7 +9472,7 @@
       <c r="I49" t="n">
         <v>6.63</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K49" t="n">
@@ -9473,13 +9485,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9506,7 +9518,7 @@
       <c r="I50" t="n">
         <v>6</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="K50" t="n">
@@ -9519,13 +9531,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9552,7 +9564,7 @@
       <c r="I51" t="n">
         <v>5.87</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K51" t="n">
@@ -9565,13 +9577,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9598,7 +9610,7 @@
       <c r="I52" t="n">
         <v>5.33</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K52" t="n">
@@ -9611,13 +9623,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9644,7 +9656,7 @@
       <c r="I53" t="n">
         <v>5.35</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K53" t="n">
@@ -9657,13 +9669,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9690,7 +9702,7 @@
       <c r="I54" t="n">
         <v>6.779999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9703,13 +9715,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9736,7 +9748,7 @@
       <c r="I55" t="n">
         <v>7.29</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K55" t="n">
@@ -9749,13 +9761,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9782,7 +9794,7 @@
       <c r="I56" t="n">
         <v>7.640000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9795,13 +9807,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9828,7 +9840,7 @@
       <c r="I57" t="n">
         <v>8.040000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K57" t="n">
@@ -9841,13 +9853,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9874,7 +9886,7 @@
       <c r="I58" t="n">
         <v>7.33</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9887,13 +9899,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9920,7 +9932,7 @@
       <c r="I59" t="n">
         <v>7.4</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K59" t="n">
@@ -9933,13 +9945,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9966,7 +9978,7 @@
       <c r="I60" t="n">
         <v>7.88</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K60" t="n">
@@ -9979,13 +9991,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10012,7 +10024,7 @@
       <c r="I61" t="n">
         <v>8.200000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K61" t="n">
@@ -10025,13 +10037,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10058,7 +10070,7 @@
       <c r="I62" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K62" t="n">
@@ -10071,13 +10083,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10104,7 +10116,7 @@
       <c r="I63" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K63" t="n">
@@ -10117,13 +10129,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10150,7 +10162,7 @@
       <c r="I64" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10163,13 +10175,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10196,7 +10208,7 @@
       <c r="I65" t="n">
         <v>9.059999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K65" t="n">
@@ -10209,13 +10221,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10242,7 +10254,7 @@
       <c r="I66" t="n">
         <v>9.499999999999998</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="K66" t="n">
@@ -10255,13 +10267,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10288,7 +10300,7 @@
       <c r="I67" t="n">
         <v>9.67</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K67" t="n">
@@ -10301,13 +10313,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10334,7 +10346,7 @@
       <c r="I68" t="n">
         <v>9.940000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="K68" t="n">
@@ -10347,13 +10359,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10380,7 +10392,7 @@
       <c r="I69" t="n">
         <v>10.33</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="K69" t="n">
@@ -10393,13 +10405,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10426,7 +10438,7 @@
       <c r="I70" t="n">
         <v>10.32</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K70" t="n">
@@ -10439,13 +10451,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10472,7 +10484,7 @@
       <c r="I71" t="n">
         <v>11.16</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="K71" t="n">
@@ -10485,13 +10497,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10518,7 +10530,7 @@
       <c r="I72" t="n">
         <v>11.72</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="K72" t="n">
@@ -10531,13 +10543,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10564,7 +10576,7 @@
       <c r="I73" t="n">
         <v>11.79</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="K73" t="n">
@@ -10602,57 +10614,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40060</v>
       </c>
       <c r="C2" t="n">
@@ -10686,10 +10698,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40060</v>
       </c>
       <c r="C3" t="n">
@@ -10723,10 +10735,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C4" t="n">
@@ -10760,10 +10772,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C5" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39447</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C6" t="n">
@@ -10834,10 +10846,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C7" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C8" t="n">
@@ -10908,10 +10920,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C9" t="n">
@@ -10945,10 +10957,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C10" t="n">
@@ -10982,10 +10994,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C11" t="n">
@@ -11019,10 +11031,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C12" t="n">
@@ -11056,10 +11068,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C13" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C14" t="n">
@@ -11130,10 +11142,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C15" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="C16" t="n">
@@ -11204,10 +11216,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C17" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C18" t="n">
@@ -11278,10 +11290,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C19" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="C20" t="n">
@@ -11352,10 +11364,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C21" t="n">
@@ -11389,10 +11401,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C22" t="n">
@@ -11426,10 +11438,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C23" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="C24" t="n">
@@ -11500,10 +11512,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="C25" t="n">
@@ -11537,10 +11549,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C26" t="n">
@@ -11574,10 +11586,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="C27" t="n">
@@ -11611,10 +11623,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C28" t="n">
@@ -11648,10 +11660,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="C29" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C30" t="n">
@@ -11722,10 +11734,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C31" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C32" t="n">
@@ -11796,10 +11808,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C33" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C34" t="n">
@@ -11870,10 +11882,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C35" t="n">
@@ -11907,10 +11919,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C36" t="n">
@@ -11944,10 +11956,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="C37" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C38" t="n">
@@ -12018,10 +12030,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C39" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C40" t="n">
@@ -12092,10 +12104,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C41" t="n">
@@ -12129,10 +12141,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C42" t="n">
@@ -12166,10 +12178,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C43" t="n">
@@ -12203,10 +12215,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C44" t="n">
@@ -12240,10 +12252,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C45" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C46" t="n">
@@ -12314,10 +12326,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C47" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C48" t="n">
@@ -12388,10 +12400,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="C49" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C50" t="n">
@@ -12462,10 +12474,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C51" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="C52" t="n">
@@ -12536,10 +12548,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C53" t="n">
@@ -12573,10 +12585,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C54" t="n">
@@ -12610,10 +12622,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C55" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C56" t="n">
@@ -12684,10 +12696,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C57" t="n">
@@ -12721,10 +12733,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C58" t="n">
@@ -12758,10 +12770,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C59" t="n">
@@ -12795,10 +12807,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C60" t="n">
@@ -12832,10 +12844,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C61" t="n">
@@ -12869,10 +12881,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C62" t="n">
@@ -12906,10 +12918,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C63" t="n">
@@ -12943,10 +12955,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C64" t="n">
@@ -12980,10 +12992,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C65" t="n">
@@ -13017,10 +13029,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C66" t="n">
@@ -13054,10 +13066,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C67" t="n">
@@ -13091,10 +13103,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="C68" t="n">
@@ -13128,10 +13140,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C69" t="n">
@@ -13165,10 +13177,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="C70" t="n">
@@ -13202,10 +13214,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="C71" t="n">
@@ -13239,10 +13251,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C72" t="n">
@@ -13276,10 +13288,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C73" t="n">
@@ -13313,10 +13325,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="C74" t="n">
@@ -13350,10 +13362,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="C75" t="n">
@@ -13405,12 +13417,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CME.xlsx
+++ b/salidas/empresas/CME.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.17296600341797</v>
+        <v>41.17297744750977</v>
       </c>
       <c r="C2" t="n">
         <v>84.65000152587891</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>41.40158462524414</v>
+        <v>41.40158081054688</v>
       </c>
       <c r="C3" t="n">
         <v>85.12000274658203</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>43.59689331054688</v>
+        <v>43.59690475463867</v>
       </c>
       <c r="C4" t="n">
         <v>89.5</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.99287033081055</v>
+        <v>42.99288177490234</v>
       </c>
       <c r="C6" t="n">
         <v>88.26000213623047</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>47.91795349121094</v>
+        <v>47.91798782348633</v>
       </c>
       <c r="C7" t="n">
         <v>98.23000335693359</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>44.99596786499023</v>
+        <v>44.9959602355957</v>
       </c>
       <c r="C8" t="n">
         <v>92.23999786376953</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>42.92763519287109</v>
+        <v>42.92763900756836</v>
       </c>
       <c r="C9" t="n">
         <v>88</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>46.72565078735352</v>
+        <v>46.72565460205078</v>
       </c>
       <c r="C10" t="n">
         <v>95.65000152587891</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>48.94834899902344</v>
+        <v>48.9483528137207</v>
       </c>
       <c r="C11" t="n">
         <v>100.1999969482422</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>52.32881927490234</v>
+        <v>52.32882308959961</v>
       </c>
       <c r="C12" t="n">
         <v>107.120002746582</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>49.86121368408203</v>
+        <v>49.86122131347656</v>
       </c>
       <c r="C13" t="n">
         <v>101.9499969482422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>55.09920883178711</v>
+        <v>55.09920501708984</v>
       </c>
       <c r="C14" t="n">
         <v>112.6600036621094</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>52.73698425292969</v>
+        <v>52.73699188232422</v>
       </c>
       <c r="C15" t="n">
         <v>107.8300018310547</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>52.16205978393555</v>
+        <v>52.16204833984375</v>
       </c>
       <c r="C16" t="n">
         <v>106.4919967651367</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>50.62305068969727</v>
+        <v>50.6230354309082</v>
       </c>
       <c r="C17" t="n">
         <v>103.3499984741211</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>52.01901245117188</v>
+        <v>52.0190315246582</v>
       </c>
       <c r="C18" t="n">
         <v>106.1999969482422</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>52.43181610107422</v>
+        <v>52.43183517456055</v>
       </c>
       <c r="C19" t="n">
         <v>106.8720016479492</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>54.21170043945312</v>
+        <v>54.21171569824219</v>
       </c>
       <c r="C20" t="n">
         <v>110.5</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>54.43739318847656</v>
+        <v>54.43737030029297</v>
       </c>
       <c r="C21" t="n">
         <v>110.9599990844727</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>57.71917343139648</v>
+        <v>57.71914291381836</v>
       </c>
       <c r="C22" t="n">
         <v>117.4700012207031</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>65.47271728515625</v>
+        <v>65.47272491455078</v>
       </c>
       <c r="C23" t="n">
         <v>133.25</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>64.72095489501953</v>
+        <v>64.72091674804688</v>
       </c>
       <c r="C24" t="n">
         <v>131.7200012207031</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>67.49676513671875</v>
+        <v>67.49678802490234</v>
       </c>
       <c r="C25" t="n">
         <v>137.1999969482422</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>60.74710845947266</v>
+        <v>60.74711227416992</v>
       </c>
       <c r="C26" t="n">
         <v>123.4800033569336</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>50.50452423095703</v>
+        <v>50.50453186035156</v>
       </c>
       <c r="C27" t="n">
         <v>102.6600036621094</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>46.25820541381836</v>
+        <v>46.25820922851562</v>
       </c>
       <c r="C28" t="n">
         <v>93.81999969482422</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>45.10939407348633</v>
+        <v>45.10940551757812</v>
       </c>
       <c r="C29" t="n">
         <v>91.48999786376953</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>42.43212509155273</v>
+        <v>42.43212127685547</v>
       </c>
       <c r="C30" t="n">
         <v>86.05999755859375</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>37.89484786987305</v>
+        <v>37.89484024047852</v>
       </c>
       <c r="C31" t="n">
         <v>76.63800048828125</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>35.61436080932617</v>
+        <v>35.6143684387207</v>
       </c>
       <c r="C32" t="n">
         <v>72.0260009765625</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>33.1667594909668</v>
+        <v>33.16676712036133</v>
       </c>
       <c r="C33" t="n">
         <v>67.07599639892578</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.34014129638672</v>
+        <v>37.34013748168945</v>
       </c>
       <c r="C34" t="n">
         <v>74.302001953125</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.35863494873047</v>
+        <v>28.3586368560791</v>
       </c>
       <c r="C35" t="n">
         <v>56.43000030517578</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.30290222167969</v>
+        <v>21.30289649963379</v>
       </c>
       <c r="C36" t="n">
         <v>42.38999938964844</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>21.04132080078125</v>
+        <v>21.04131126403809</v>
       </c>
       <c r="C37" t="n">
         <v>41.62200164794922</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.58346366882324</v>
+        <v>17.58345985412598</v>
       </c>
       <c r="C38" t="n">
         <v>34.78200149536133</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>25.0697135925293</v>
+        <v>25.06970977783203</v>
       </c>
       <c r="C40" t="n">
         <v>49.27799987792969</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>22.52193450927734</v>
+        <v>22.52193832397461</v>
       </c>
       <c r="C41" t="n">
         <v>44.27000045776367</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>32.72625732421875</v>
+        <v>32.72626495361328</v>
       </c>
       <c r="C42" t="n">
         <v>64.3280029296875</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.4681568145752</v>
+        <v>28.46817207336426</v>
       </c>
       <c r="C44" t="n">
         <v>55.76599884033203</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>29.71479415893555</v>
+        <v>29.71478652954102</v>
       </c>
       <c r="C45" t="n">
         <v>58.20800018310547</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>31.60013198852539</v>
+        <v>31.60012626647949</v>
       </c>
       <c r="C46" t="n">
         <v>61.63800048828125</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>31.02798271179199</v>
+        <v>31.02797698974609</v>
       </c>
       <c r="C47" t="n">
         <v>60.52199935913086</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>33.65492248535156</v>
+        <v>33.65492630004883</v>
       </c>
       <c r="C48" t="n">
         <v>65.64600372314453</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>29.5138111114502</v>
+        <v>29.51382255554199</v>
       </c>
       <c r="C50" t="n">
         <v>57.36399841308594</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>31.0439453125</v>
+        <v>31.04394912719727</v>
       </c>
       <c r="C51" t="n">
         <v>60.3380012512207</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.64884185791016</v>
+        <v>32.64883422851562</v>
       </c>
       <c r="C52" t="n">
         <v>63.22200012207031</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>34.00804138183594</v>
+        <v>34.00802993774414</v>
       </c>
       <c r="C53" t="n">
         <v>65.85399627685547</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.70462417602539</v>
+        <v>32.70460891723633</v>
       </c>
       <c r="C54" t="n">
         <v>63.33000183105469</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>29.19142913818359</v>
+        <v>29.19144248962402</v>
       </c>
       <c r="C55" t="n">
         <v>56.31000137329102</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>28.90630340576172</v>
+        <v>28.90632057189941</v>
       </c>
       <c r="C56" t="n">
         <v>55.7599983215332</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.72951889038086</v>
+        <v>25.72952461242676</v>
       </c>
       <c r="C57" t="n">
         <v>49.63199996948242</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.12444877624512</v>
+        <v>27.12446212768555</v>
       </c>
       <c r="C58" t="n">
         <v>52.09000015258789</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.16548347473145</v>
+        <v>30.16547393798828</v>
       </c>
       <c r="C59" t="n">
         <v>57.93000030517578</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>29.99989891052246</v>
+        <v>29.99989128112793</v>
       </c>
       <c r="C60" t="n">
         <v>57.61199951171875</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>32.25298690795898</v>
+        <v>32.25297546386719</v>
       </c>
       <c r="C62" t="n">
         <v>61.71200180053711</v>
@@ -1788,7 +1788,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>31.66614532470703</v>
+        <v>31.6661434173584</v>
       </c>
       <c r="C64" t="n">
         <v>60.31000137329102</v>
@@ -1817,7 +1817,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>31.05917739868164</v>
+        <v>31.05918502807617</v>
       </c>
       <c r="C65" t="n">
         <v>59.15399932861328</v>
@@ -1846,7 +1846,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>30.00801467895508</v>
+        <v>30.00801277160645</v>
       </c>
       <c r="C66" t="n">
         <v>57.15200042724609</v>
@@ -1875,7 +1875,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.77914237976074</v>
+        <v>30.77914810180664</v>
       </c>
       <c r="C67" t="n">
         <v>58.31800079345703</v>
@@ -1904,7 +1904,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>30.52579689025879</v>
+        <v>30.52581024169922</v>
       </c>
       <c r="C68" t="n">
         <v>57.8380012512207</v>
@@ -1933,7 +1933,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>28.19618034362793</v>
+        <v>28.1961784362793</v>
       </c>
       <c r="C69" t="n">
         <v>53.42399978637695</v>
@@ -1962,7 +1962,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>26.15276145935059</v>
+        <v>26.15275764465332</v>
       </c>
       <c r="C70" t="n">
         <v>49.27999877929688</v>
@@ -1991,7 +1991,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>29.24777793884277</v>
+        <v>29.24778938293457</v>
       </c>
       <c r="C71" t="n">
         <v>55.11199951171875</v>
@@ -2020,7 +2020,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>26.45843887329102</v>
+        <v>26.45845413208008</v>
       </c>
       <c r="C72" t="n">
         <v>49.85599899291992</v>
@@ -2049,7 +2049,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>26.01545524597168</v>
+        <v>26.01546287536621</v>
       </c>
       <c r="C73" t="n">
         <v>48.73400115966797</v>
@@ -2078,7 +2078,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>25.57131195068359</v>
+        <v>25.57131958007812</v>
       </c>
       <c r="C74" t="n">
         <v>47.90200042724609</v>
@@ -2107,7 +2107,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>30.90746116638184</v>
+        <v>30.90744590759277</v>
       </c>
       <c r="C75" t="n">
         <v>57.89799880981445</v>
@@ -2136,7 +2136,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>31.4893798828125</v>
+        <v>31.4893913269043</v>
       </c>
       <c r="C76" t="n">
         <v>57.86600112915039</v>
@@ -2165,7 +2165,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>28.93065071105957</v>
+        <v>28.93065643310547</v>
       </c>
       <c r="C77" t="n">
         <v>53.16400146484375</v>
@@ -2194,7 +2194,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>28.03276634216309</v>
+        <v>28.03276443481445</v>
       </c>
       <c r="C78" t="n">
         <v>51.51399993896484</v>
@@ -2223,7 +2223,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>29.4245662689209</v>
+        <v>29.4245548248291</v>
       </c>
       <c r="C79" t="n">
         <v>53.62200164794922</v>
@@ -2252,7 +2252,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>28.59485816955566</v>
+        <v>28.59486961364746</v>
       </c>
       <c r="C80" t="n">
         <v>52.11000061035156</v>
@@ -2281,7 +2281,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>30.12584686279297</v>
+        <v>30.12586212158203</v>
       </c>
       <c r="C81" t="n">
         <v>54.90000152587891</v>
@@ -2339,7 +2339,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>30.94280242919922</v>
+        <v>30.94279861450195</v>
       </c>
       <c r="C83" t="n">
         <v>55.93000030517578</v>
@@ -2368,7 +2368,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>30.57765007019043</v>
+        <v>30.57767295837402</v>
       </c>
       <c r="C84" t="n">
         <v>55.27000045776367</v>
@@ -2397,7 +2397,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>28.97868347167969</v>
+        <v>28.97868919372559</v>
       </c>
       <c r="C85" t="n">
         <v>50.66999816894531</v>
@@ -2426,7 +2426,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>33.07928848266602</v>
+        <v>33.07928085327148</v>
       </c>
       <c r="C86" t="n">
         <v>57.84000015258789</v>
@@ -2455,7 +2455,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>34.12587738037109</v>
+        <v>34.1258659362793</v>
       </c>
       <c r="C87" t="n">
         <v>59.66999816894531</v>
@@ -2484,7 +2484,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>35.37931442260742</v>
+        <v>35.37933731079102</v>
       </c>
       <c r="C88" t="n">
         <v>61.40999984741211</v>
@@ -2513,7 +2513,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>35.06245803833008</v>
+        <v>35.06246948242188</v>
       </c>
       <c r="C89" t="n">
         <v>60.86000061035156</v>
@@ -2542,7 +2542,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>39.13561248779297</v>
+        <v>39.13561630249023</v>
       </c>
       <c r="C90" t="n">
         <v>67.93000030517578</v>
@@ -2571,7 +2571,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>44.04216003417969</v>
+        <v>44.04217529296875</v>
       </c>
       <c r="C91" t="n">
         <v>75.94999694824219</v>
@@ -2600,7 +2600,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>42.94620513916016</v>
+        <v>42.94620132446289</v>
       </c>
       <c r="C92" t="n">
         <v>74.05999755859375</v>
@@ -2629,7 +2629,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>41.23552703857422</v>
+        <v>41.23551940917969</v>
       </c>
       <c r="C93" t="n">
         <v>71.11000061035156</v>
@@ -2658,7 +2658,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>43.1061897277832</v>
+        <v>43.10618591308594</v>
       </c>
       <c r="C94" t="n">
         <v>73.87999725341797</v>
@@ -2687,7 +2687,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>43.29874038696289</v>
+        <v>43.29875183105469</v>
       </c>
       <c r="C95" t="n">
         <v>74.20999908447266</v>
@@ -2716,7 +2716,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>47.81473159790039</v>
+        <v>47.81474685668945</v>
       </c>
       <c r="C96" t="n">
         <v>81.94999694824219</v>
@@ -2774,7 +2774,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>45.28575134277344</v>
+        <v>45.28572463989258</v>
       </c>
       <c r="C98" t="n">
         <v>74.76000213623047</v>
@@ -2803,7 +2803,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>44.7163200378418</v>
+        <v>44.71632385253906</v>
       </c>
       <c r="C99" t="n">
         <v>73.81999969482422</v>
@@ -2832,7 +2832,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>45.11493682861328</v>
+        <v>45.11494064331055</v>
       </c>
       <c r="C100" t="n">
         <v>74.01999664306641</v>
@@ -2861,7 +2861,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>42.90246200561523</v>
+        <v>42.9024658203125</v>
       </c>
       <c r="C101" t="n">
         <v>70.38999938964844</v>
@@ -2919,7 +2919,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>43.53817749023438</v>
+        <v>43.53818130493164</v>
       </c>
       <c r="C103" t="n">
         <v>70.94999694824219</v>
@@ -2948,7 +2948,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>45.37298202514648</v>
+        <v>45.37297058105469</v>
       </c>
       <c r="C104" t="n">
         <v>73.94000244140625</v>
@@ -2977,7 +2977,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>46.97460174560547</v>
+        <v>46.9745979309082</v>
       </c>
       <c r="C105" t="n">
         <v>76.55000305175781</v>
@@ -3006,7 +3006,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>49.37063598632812</v>
+        <v>49.37065887451172</v>
       </c>
       <c r="C106" t="n">
         <v>79.95999908447266</v>
@@ -3035,7 +3035,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>51.74779510498047</v>
+        <v>51.74779891967773</v>
       </c>
       <c r="C107" t="n">
         <v>83.80999755859375</v>
@@ -3064,7 +3064,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.26028060913086</v>
+        <v>52.2602653503418</v>
       </c>
       <c r="C108" t="n">
         <v>84.63999938964844</v>
@@ -3093,7 +3093,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>56.24079513549805</v>
+        <v>56.24078369140625</v>
       </c>
       <c r="C109" t="n">
         <v>88.65000152587891</v>
@@ -3122,7 +3122,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>54.11551284790039</v>
+        <v>54.11548614501953</v>
       </c>
       <c r="C110" t="n">
         <v>85.30000305175781</v>
@@ -3151,7 +3151,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>60.85933685302734</v>
+        <v>60.85935211181641</v>
       </c>
       <c r="C111" t="n">
         <v>95.93000030517578</v>
@@ -3180,7 +3180,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>60.39723968505859</v>
+        <v>60.39724349975586</v>
       </c>
       <c r="C112" t="n">
         <v>94.70999908447266</v>
@@ -3209,7 +3209,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>57.97393035888672</v>
+        <v>57.97394943237305</v>
       </c>
       <c r="C113" t="n">
         <v>90.91000366210938</v>
@@ -3238,7 +3238,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>60.07201766967773</v>
+        <v>60.07201385498047</v>
       </c>
       <c r="C114" t="n">
         <v>94.19999694824219</v>
@@ -3267,7 +3267,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>59.65588760375977</v>
+        <v>59.65590286254883</v>
       </c>
       <c r="C115" t="n">
         <v>93.05999755859375</v>
@@ -3296,7 +3296,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>61.56621932983398</v>
+        <v>61.56624984741211</v>
       </c>
       <c r="C116" t="n">
         <v>96.04000091552734</v>
@@ -3325,7 +3325,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>60.54053497314453</v>
+        <v>60.54054260253906</v>
       </c>
       <c r="C117" t="n">
         <v>94.44000244140625</v>
@@ -3383,7 +3383,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>60.88915252685547</v>
+        <v>60.88916397094727</v>
       </c>
       <c r="C119" t="n">
         <v>94.47000122070312</v>
@@ -3412,7 +3412,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>62.93876647949219</v>
+        <v>62.93875503540039</v>
       </c>
       <c r="C120" t="n">
         <v>97.65000152587891</v>
@@ -3441,7 +3441,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>60.54383087158203</v>
+        <v>60.54383850097656</v>
       </c>
       <c r="C121" t="n">
         <v>90.59999847412109</v>
@@ -3470,7 +3470,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>60.04262924194336</v>
+        <v>60.04265594482422</v>
       </c>
       <c r="C122" t="n">
         <v>89.84999847412109</v>
@@ -3499,7 +3499,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>61.10517883300781</v>
+        <v>61.10515975952148</v>
       </c>
       <c r="C123" t="n">
         <v>91.44000244140625</v>
@@ -3557,7 +3557,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>61.81561660766602</v>
+        <v>61.81555938720703</v>
       </c>
       <c r="C125" t="n">
         <v>91.91000366210938</v>
@@ -3615,7 +3615,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>65.91982269287109</v>
+        <v>65.91980743408203</v>
       </c>
       <c r="C127" t="n">
         <v>97.40000152587891</v>
@@ -3644,7 +3644,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>69.19550323486328</v>
+        <v>69.19548034667969</v>
       </c>
       <c r="C128" t="n">
         <v>102.2399978637695</v>
@@ -3673,7 +3673,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>73.33072662353516</v>
+        <v>73.33070373535156</v>
       </c>
       <c r="C129" t="n">
         <v>108.3499984741211</v>
@@ -3702,7 +3702,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>71.13487243652344</v>
+        <v>71.13486480712891</v>
       </c>
       <c r="C130" t="n">
         <v>104.5199966430664</v>
@@ -3731,7 +3731,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>68.12667846679688</v>
+        <v>68.12669372558594</v>
       </c>
       <c r="C131" t="n">
         <v>100.0999984741211</v>
@@ -3760,7 +3760,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>76.84503936767578</v>
+        <v>76.84499359130859</v>
       </c>
       <c r="C132" t="n">
         <v>112.9100036621094</v>
@@ -3789,7 +3789,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>81.08665466308594</v>
+        <v>81.08669281005859</v>
       </c>
       <c r="C133" t="n">
         <v>115.3499984741211</v>
@@ -3818,7 +3818,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>85.11463165283203</v>
+        <v>85.11465454101562</v>
       </c>
       <c r="C134" t="n">
         <v>121.0800018310547</v>
@@ -3876,7 +3876,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>83.96038818359375</v>
+        <v>83.96036529541016</v>
       </c>
       <c r="C136" t="n">
         <v>118.8000030517578</v>
@@ -3905,7 +3905,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>82.11579132080078</v>
+        <v>82.11579895019531</v>
       </c>
       <c r="C137" t="n">
         <v>116.1900024414062</v>
@@ -3934,7 +3934,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>82.89319610595703</v>
+        <v>82.89318084716797</v>
       </c>
       <c r="C138" t="n">
         <v>117.2900009155273</v>
@@ -3963,7 +3963,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>89.012939453125</v>
+        <v>89.01291656494141</v>
       </c>
       <c r="C139" t="n">
         <v>125.2399978637695</v>
@@ -3992,7 +3992,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>87.15079498291016</v>
+        <v>87.15078735351562</v>
       </c>
       <c r="C140" t="n">
         <v>122.620002746582</v>
@@ -4050,7 +4050,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>96.93119812011719</v>
+        <v>96.93119049072266</v>
       </c>
       <c r="C142" t="n">
         <v>135.6799926757812</v>
@@ -4079,7 +4079,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>97.99568939208984</v>
+        <v>97.99567413330078</v>
       </c>
       <c r="C143" t="n">
         <v>137.1699981689453</v>
@@ -4108,7 +4108,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>106.8329162597656</v>
+        <v>106.8329315185547</v>
       </c>
       <c r="C144" t="n">
         <v>149.5399932861328</v>
@@ -4137,7 +4137,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>107.3142700195312</v>
+        <v>107.3142547607422</v>
       </c>
       <c r="C145" t="n">
         <v>146.0500030517578</v>
@@ -4166,7 +4166,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>112.7736511230469</v>
+        <v>112.773681640625</v>
       </c>
       <c r="C146" t="n">
         <v>153.4799957275391</v>
@@ -4195,7 +4195,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>122.0906753540039</v>
+        <v>122.0905990600586</v>
       </c>
       <c r="C147" t="n">
         <v>166.1600036621094</v>
@@ -4224,7 +4224,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>119.3384552001953</v>
+        <v>119.3384628295898</v>
       </c>
       <c r="C148" t="n">
         <v>161.7400054931641</v>
@@ -4253,7 +4253,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>116.3428039550781</v>
+        <v>116.3428268432617</v>
       </c>
       <c r="C149" t="n">
         <v>157.6799926757812</v>
@@ -4282,7 +4282,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>120.1943588256836</v>
+        <v>120.1943435668945</v>
       </c>
       <c r="C150" t="n">
         <v>162.8999938964844</v>
@@ -4311,7 +4311,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>121.4367141723633</v>
+        <v>121.4368133544922</v>
       </c>
       <c r="C151" t="n">
         <v>163.9199981689453</v>
@@ -4340,7 +4340,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>117.8807754516602</v>
+        <v>117.8807601928711</v>
       </c>
       <c r="C152" t="n">
         <v>159.1199951171875</v>
@@ -4369,7 +4369,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>129.4451904296875</v>
+        <v>129.4451446533203</v>
       </c>
       <c r="C153" t="n">
         <v>174.7299957275391</v>
@@ -4398,7 +4398,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>126.607421875</v>
+        <v>126.6073913574219</v>
       </c>
       <c r="C154" t="n">
         <v>170.2100067138672</v>
@@ -4427,7 +4427,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>136.2995147705078</v>
+        <v>136.2994995117188</v>
       </c>
       <c r="C155" t="n">
         <v>183.2400054931641</v>
@@ -4456,7 +4456,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>141.3872985839844</v>
+        <v>141.3872833251953</v>
       </c>
       <c r="C156" t="n">
         <v>190.0800018310547</v>
@@ -4485,7 +4485,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>141.8106994628906</v>
+        <v>141.8106384277344</v>
       </c>
       <c r="C157" t="n">
         <v>188.1199951171875</v>
@@ -4514,7 +4514,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>137.4083099365234</v>
+        <v>137.4083557128906</v>
       </c>
       <c r="C158" t="n">
         <v>182.2799987792969</v>
@@ -4601,7 +4601,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>135.4433441162109</v>
+        <v>135.4433898925781</v>
       </c>
       <c r="C161" t="n">
         <v>178.8999938964844</v>
@@ -4630,7 +4630,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>145.4520721435547</v>
+        <v>145.4520874023438</v>
       </c>
       <c r="C162" t="n">
         <v>192.1199951171875</v>
@@ -4659,7 +4659,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>147.5093536376953</v>
+        <v>147.5093688964844</v>
       </c>
       <c r="C163" t="n">
         <v>194.1100006103516</v>
@@ -4688,7 +4688,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>147.7449340820312</v>
+        <v>147.7449645996094</v>
       </c>
       <c r="C164" t="n">
         <v>194.4199981689453</v>
@@ -4717,7 +4717,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>165.1244506835938</v>
+        <v>165.12451171875</v>
       </c>
       <c r="C165" t="n">
         <v>217.2899932861328</v>
@@ -4746,7 +4746,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>161.1447296142578</v>
+        <v>161.1447448730469</v>
       </c>
       <c r="C166" t="n">
         <v>211.3399963378906</v>
@@ -4804,7 +4804,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>154.5796508789062</v>
+        <v>154.5796813964844</v>
       </c>
       <c r="C168" t="n">
         <v>202.7299957275391</v>
@@ -4833,7 +4833,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>155.5182952880859</v>
+        <v>155.518310546875</v>
       </c>
       <c r="C169" t="n">
         <v>200.7200012207031</v>
@@ -4862,7 +4862,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>168.2173004150391</v>
+        <v>168.21728515625</v>
       </c>
       <c r="C170" t="n">
         <v>217.1100006103516</v>
@@ -4891,7 +4891,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>154.0461730957031</v>
+        <v>154.0461578369141</v>
       </c>
       <c r="C171" t="n">
         <v>198.8200073242188</v>
@@ -4949,7 +4949,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>138.6223754882812</v>
+        <v>138.6223602294922</v>
       </c>
       <c r="C173" t="n">
         <v>178.2100067138672</v>
@@ -4978,7 +4978,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>142.0371856689453</v>
+        <v>142.0372161865234</v>
       </c>
       <c r="C174" t="n">
         <v>182.6000061035156</v>
@@ -5007,7 +5007,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>126.9962005615234</v>
+        <v>126.9962615966797</v>
       </c>
       <c r="C175" t="n">
         <v>162.5399932861328</v>
@@ -5094,7 +5094,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>131.3919677734375</v>
+        <v>131.3919372558594</v>
       </c>
       <c r="C178" t="n">
         <v>167.3099975585938</v>
@@ -5123,7 +5123,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>118.3634490966797</v>
+        <v>118.3634567260742</v>
       </c>
       <c r="C179" t="n">
         <v>150.7200012207031</v>
@@ -5152,7 +5152,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>137.45458984375</v>
+        <v>137.4546203613281</v>
       </c>
       <c r="C180" t="n">
         <v>175.0299987792969</v>
@@ -5181,7 +5181,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>145.6524505615234</v>
+        <v>145.6524353027344</v>
       </c>
       <c r="C181" t="n">
         <v>182.0500030517578</v>
@@ -5239,7 +5239,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>159.7736206054688</v>
+        <v>159.7736358642578</v>
       </c>
       <c r="C183" t="n">
         <v>199.6999969482422</v>
@@ -5268,7 +5268,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>164.0878448486328</v>
+        <v>164.0879211425781</v>
       </c>
       <c r="C184" t="n">
         <v>204.2299957275391</v>
@@ -5326,7 +5326,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>175.7619781494141</v>
+        <v>175.7619934082031</v>
       </c>
       <c r="C186" t="n">
         <v>218.7599945068359</v>
@@ -5355,7 +5355,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>171.5865631103516</v>
+        <v>171.5866241455078</v>
       </c>
       <c r="C187" t="n">
         <v>212.6799926757812</v>
@@ -5413,7 +5413,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>162.7442169189453</v>
+        <v>162.7442779541016</v>
       </c>
       <c r="C189" t="n">
         <v>201.7200012207031</v>
@@ -5442,7 +5442,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>156.7438049316406</v>
+        <v>156.7437591552734</v>
       </c>
       <c r="C190" t="n">
         <v>193.3800048828125</v>
@@ -5500,7 +5500,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>178.7420806884766</v>
+        <v>178.7420501708984</v>
       </c>
       <c r="C192" t="n">
         <v>220.5200042724609</v>
@@ -5558,7 +5558,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>189.4342651367188</v>
+        <v>189.4342803955078</v>
       </c>
       <c r="C194" t="n">
         <v>229.5</v>
@@ -5587,7 +5587,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>195.2369842529297</v>
+        <v>195.2369537353516</v>
       </c>
       <c r="C195" t="n">
         <v>236.5299987792969</v>
@@ -5616,7 +5616,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>197.2202606201172</v>
+        <v>197.2201995849609</v>
       </c>
       <c r="C196" t="n">
         <v>237.8600006103516</v>
@@ -5645,7 +5645,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>181.864501953125</v>
+        <v>181.8644561767578</v>
       </c>
       <c r="C197" t="n">
         <v>219.3399963378906</v>
@@ -5674,7 +5674,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>164.8587493896484</v>
+        <v>164.8587341308594</v>
       </c>
       <c r="C198" t="n">
         <v>198.8300018310547</v>
@@ -5703,7 +5703,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>170.5805969238281</v>
+        <v>170.58056640625</v>
       </c>
       <c r="C199" t="n">
         <v>204.6999969482422</v>
@@ -5732,7 +5732,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>166.2306365966797</v>
+        <v>166.2306060791016</v>
       </c>
       <c r="C200" t="n">
         <v>199.4799957275391</v>
@@ -5761,7 +5761,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>163.0056762695312</v>
+        <v>163.0057067871094</v>
       </c>
       <c r="C201" t="n">
         <v>195.6100006103516</v>
@@ -5848,7 +5848,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>147.8187866210938</v>
+        <v>147.8187561035156</v>
       </c>
       <c r="C204" t="n">
         <v>176.5</v>
@@ -5877,7 +5877,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>145.4140930175781</v>
+        <v>145.4140472412109</v>
       </c>
       <c r="C205" t="n">
         <v>168.1600036621094</v>
@@ -5906,7 +5906,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>152.7643127441406</v>
+        <v>152.7643280029297</v>
       </c>
       <c r="C206" t="n">
         <v>176.6600036621094</v>
@@ -5935,7 +5935,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>160.2875213623047</v>
+        <v>160.2875366210938</v>
       </c>
       <c r="C207" t="n">
         <v>185.3600006103516</v>
@@ -5964,7 +5964,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>166.6217956542969</v>
+        <v>166.6217498779297</v>
       </c>
       <c r="C208" t="n">
         <v>191.5200042724609</v>
@@ -5993,7 +5993,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>161.6193084716797</v>
+        <v>161.6193237304688</v>
       </c>
       <c r="C209" t="n">
         <v>185.7700042724609</v>
@@ -6022,7 +6022,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>155.5119018554688</v>
+        <v>155.5119171142578</v>
       </c>
       <c r="C210" t="n">
         <v>178.75</v>
@@ -6051,7 +6051,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>162.1789398193359</v>
+        <v>162.178955078125</v>
       </c>
       <c r="C211" t="n">
         <v>185.2899932861328</v>
@@ -6080,7 +6080,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>174.1438598632812</v>
+        <v>174.1438751220703</v>
       </c>
       <c r="C212" t="n">
         <v>198.9600067138672</v>
@@ -6138,7 +6138,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>176.1984100341797</v>
+        <v>176.1983947753906</v>
       </c>
       <c r="C214" t="n">
         <v>200.2200012207031</v>
@@ -6196,7 +6196,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>192.1620635986328</v>
+        <v>192.1620483398438</v>
       </c>
       <c r="C216" t="n">
         <v>218.3600006103516</v>
@@ -6225,7 +6225,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>190.9567565917969</v>
+        <v>190.9567413330078</v>
       </c>
       <c r="C217" t="n">
         <v>210.6000061035156</v>
@@ -6312,7 +6312,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>196.2365112304688</v>
+        <v>196.2365417480469</v>
       </c>
       <c r="C220" t="n">
         <v>215.2899932861328</v>
@@ -6370,7 +6370,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>185.0159912109375</v>
+        <v>185.0159759521484</v>
       </c>
       <c r="C222" t="n">
         <v>202.9799957275391</v>
@@ -6428,7 +6428,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>177.5799560546875</v>
+        <v>177.5799255371094</v>
       </c>
       <c r="C224" t="n">
         <v>193.7100067138672</v>
@@ -6457,7 +6457,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>197.7755279541016</v>
+        <v>197.7754974365234</v>
       </c>
       <c r="C225" t="n">
         <v>215.7400054931641</v>
@@ -6486,7 +6486,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>203.3371429443359</v>
+        <v>203.3371276855469</v>
       </c>
       <c r="C226" t="n">
         <v>220.6499938964844</v>
@@ -6544,7 +6544,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>219.3258361816406</v>
+        <v>219.3258209228516</v>
       </c>
       <c r="C228" t="n">
         <v>238</v>
@@ -6573,7 +6573,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>220.3851776123047</v>
+        <v>220.3851623535156</v>
       </c>
       <c r="C229" t="n">
         <v>232.2299957275391</v>
@@ -6602,7 +6602,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>224.4563903808594</v>
+        <v>224.4563598632812</v>
       </c>
       <c r="C230" t="n">
         <v>236.5200042724609</v>
@@ -6631,7 +6631,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>240.8265533447266</v>
+        <v>240.8265380859375</v>
       </c>
       <c r="C231" t="n">
         <v>253.7700042724609</v>
@@ -6718,7 +6718,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>275.6157836914062</v>
+        <v>275.6157531738281</v>
       </c>
       <c r="C234" t="n">
         <v>289</v>
@@ -6805,7 +6805,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>255.3312072753906</v>
+        <v>255.3311767578125</v>
       </c>
       <c r="C237" t="n">
         <v>266.510009765625</v>
@@ -6892,7 +6892,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>270.9439086914062</v>
+        <v>270.9438781738281</v>
       </c>
       <c r="C240" t="n">
         <v>281.4599914550781</v>
@@ -6979,7 +6979,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>308.9804382324219</v>
+        <v>308.9804077148438</v>
       </c>
       <c r="C243" t="n">
         <v>319.5</v>
@@ -7008,7 +7008,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>292.4536743164062</v>
+        <v>292.4537048339844</v>
       </c>
       <c r="C244" t="n">
         <v>295.3500061035156</v>
@@ -7037,7 +7037,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>284.9975280761719</v>
+        <v>284.9974975585938</v>
       </c>
       <c r="C245" t="n">
         <v>287.8200073242188</v>
